--- a/files/九龙-将军澳-Grand Seasons.xlsx
+++ b/files/九龙-将军澳-Grand Seasons.xlsx
@@ -13074,7 +13074,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -29094,7 +29094,7 @@
       </c>
       <c r="G620" s="3" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H620" s="5" t="n">
@@ -33159,7 +33159,7 @@
           <t>D | 437呎 (2房)
 $627万
 $14,348/呎
-(25年-04月)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="F44" s="18" t="inlineStr">
@@ -36462,7 +36462,7 @@
           <t>C | 453呎 (2房)
 $753万
 $16,618/呎
-(25年-11月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E50" s="18" t="inlineStr">

--- a/files/九龙-将军澳-Grand Seasons.xlsx
+++ b/files/九龙-将军澳-Grand Seasons.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B座 销控表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -112,36 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -171,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -187,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1344,7 +1213,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -27254,7 +27123,7 @@
       </c>
       <c r="G580" s="3" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-02-09</t>
         </is>
       </c>
       <c r="H580" s="5" t="n">
@@ -30596,6180 +30465,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H55"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Grand Seasons - 1A座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>350 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>339 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>66/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$947万
-$21,372/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$1,034万
-$20,881/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$918万
-$20,269/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$896万
-$20,515/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$662万
-$20,486/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$650万
-$20,121/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H6" s="17" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$728万
-$22,064/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>65/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$715万
-$16,140/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$781万
-$15,784/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$717万
-$15,828/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$684万
-$15,645/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$498万
-$15,418/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$507万
-$15,684/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="H7" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$528万
-$16,003/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>63/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$714万
-$16,111/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$780万
-$15,758/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$716万
-$15,799/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$686万
-$15,705/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$503万
-$15,567/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$503万
-$15,570/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="H8" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$609万
-$18,448/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>62/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$713万
-$16,086/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$779万
-$15,731/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$714万
-$15,773/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$670万
-$15,330/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$499万
-$15,455/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$505万
-$15,628/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="H9" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$526万
-$15,945/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>61/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$711万
-$16,056/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$777万
-$15,705/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$713万
-$15,746/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$684万
-$15,652/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$496万
-$15,341/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$507万
-$15,690/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="H10" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$525万
-$15,918/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>60/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$706万
-$15,941/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$776万
-$15,677/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$712万
-$15,720/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$683万
-$15,625/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$500万
-$15,489/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$503万
-$15,576/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H11" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$524万
-$15,891/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>59/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$709万
-$16,005/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$775万
-$15,651/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$707万
-$15,607/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$678万
-$15,513/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$497万
-$15,375/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$502万
-$15,551/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H12" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$524万
-$15,864/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>58/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$704万
-$15,887/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$773万
-$15,624/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$710万
-$15,667/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$677万
-$15,487/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$496万
-$15,350/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$499万
-$15,437/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H13" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$520万
-$15,748/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>57/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$702万
-$15,835/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$771万
-$15,572/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$707万
-$15,614/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$663万
-$15,174/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$494万
-$15,297/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$494万
-$15,297/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H14" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$521万
-$15,785/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>56/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$700万
-$15,806/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$770万
-$15,545/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$702万
-$15,499/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$670万
-$15,320/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$493万
-$15,272/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$491万
-$15,189/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="H15" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$520万
-$15,761/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>55/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$687万
-$15,515/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$768万
-$15,519/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$701万
-$15,475/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$661万
-$15,121/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$490万
-$15,161/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$492万
-$15,248/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H16" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$516万
-$15,645/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>53/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$686万
-$15,490/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$767万
-$15,493/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$684万
-$15,104/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$660万
-$15,098/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$492万
-$15,220/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$489万
-$15,136/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="H17" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$512万
-$15,530/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>52/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$685万
-$15,463/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$766万
-$15,467/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$699万
-$15,422/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$659万
-$15,071/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$491万
-$15,195/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$488万
-$15,108/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="H18" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$514万
-$15,591/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>51/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$684万
-$15,436/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$764万
-$15,438/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$694万
-$15,311/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$658万
-$15,046/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$490万
-$15,167/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$487万
-$15,084/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="H19" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$514万
-$15,564/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>50/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$686万
-$15,497/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$763万
-$15,414/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$685万
-$15,113/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$656万
-$15,021/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$486万
-$15,056/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$489万
-$15,146/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="H20" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$513万
-$15,536/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>48/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$685万
-$15,472/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$762万
-$15,388/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$691万
-$15,258/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$655万
-$14,995/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$486万
-$15,031/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$486万
-$15,031/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H21" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$509万
-$15,424/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>47/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$683万
-$15,420/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$759万
-$15,335/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$677万
-$14,951/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$653万
-$14,945/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$484万
-$14,981/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$487万
-$15,068/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="H22" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$507万
-$15,373/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>46/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$682万
-$15,393/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$758万
-$15,307/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$688万
-$15,183/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$652万
-$14,920/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$483万
-$14,957/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G23" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$483万
-$14,957/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="H23" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$509万
-$15,433/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>45/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$677万
-$15,280/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$756万
-$15,281/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$675万
-$14,901/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$651万
-$14,895/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$483万
-$14,941/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G24" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$485万
-$15,025/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="H24" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$508万
-$15,406/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>43/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$680万
-$15,341/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$755万
-$15,253/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$674万
-$14,874/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$650万
-$14,867/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$482万
-$14,920/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G25" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$482万
-$14,920/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H25" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$505万
-$15,291/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>42/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$678万
-$15,312/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$754万
-$15,226/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$673万
-$14,848/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$648万
-$14,840/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$481万
-$14,901/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G26" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$481万
-$14,901/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H26" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$506万
-$15,348/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$673万
-$15,196/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$752万
-$15,198/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$671万
-$14,821/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$647万
-$14,815/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$481万
-$14,885/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G27" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$481万
-$14,885/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H27" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$506万
-$15,324/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$676万
-$15,257/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$751万
-$15,172/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$670万
-$14,795/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$646万
-$14,787/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$480万
-$14,867/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G28" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$480万
-$14,867/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H28" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$505万
-$15,297/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$671万
-$15,144/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$750万
-$15,143/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$669万
-$14,766/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$645万
-$14,760/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$480万
-$14,848/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G29" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$480万
-$14,848/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H29" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$504万
-$15,267/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$670万
-$15,115/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$748万
-$15,115/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$668万
-$14,742/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$644万
-$14,735/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="F30" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$479万
-$14,830/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="G30" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$479万
-$14,830/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H30" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$500万
-$15,155/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$667万
-$15,063/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$746万
-$15,063/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D31" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$665万
-$14,689/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="E31" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$642万
-$14,682/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="F31" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$478万
-$14,796/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G31" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$478万
-$14,796/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="H31" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$501万
-$15,185/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$666万
-$15,034/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$744万
-$15,036/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D32" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$664万
-$14,662/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$640万
-$14,654/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="F32" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$477万
-$14,768/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="G32" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$477万
-$14,768/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H32" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$497万
-$15,073/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B33" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$665万
-$15,009/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$743万
-$15,008/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="D33" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$663万
-$14,636/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="E33" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$639万
-$14,629/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="F33" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$476万
-$14,743/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="G33" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$476万
-$14,743/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="H33" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$499万
-$15,130/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$664万
-$14,982/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$742万
-$14,980/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="D34" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$662万
-$14,609/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E34" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$638万
-$14,602/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="F34" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$475万
-$14,715/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="G34" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$481万
-$14,882/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="H34" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$496万
-$15,018/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B35" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$662万
-$14,953/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$740万
-$14,954/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D35" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$661万
-$14,583/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E35" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$637万
-$14,577/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="F35" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$474万
-$14,690/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="G35" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$474万
-$14,690/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="H35" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$498万
-$15,076/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B36" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$661万
-$14,928/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$739万
-$14,927/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D36" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$659万
-$14,556/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="E36" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$636万
-$14,556/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="F36" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$474万
-$14,669/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="G36" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$474万
-$14,669/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="H36" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$494万
-$14,964/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B37" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$660万
-$14,905/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$738万
-$14,905/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D37" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$658万
-$14,536/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="E37" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$636万
-$14,549/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F37" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$474万
-$14,666/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="G37" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$474万
-$14,666/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="H37" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$493万
-$14,942/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B38" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$659万
-$14,878/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$736万
-$14,879/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="D38" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$657万
-$14,508/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E38" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$635万
-$14,531/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F38" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$472万
-$14,610/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G38" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$473万
-$14,641/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="H38" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$492万
-$14,915/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B39" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$751万
-$16,955/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C39" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$735万
-$14,851/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="D39" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$656万
-$14,483/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E39" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$634万
-$14,503/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="F39" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$471万
-$14,585/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G39" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$472万
-$14,613/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="H39" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$491万
-$14,891/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="65" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B40" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$656万
-$14,799/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C40" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$732万
-$14,798/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D40" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$654万
-$14,430/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="E40" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$632万
-$14,453/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="F40" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$470万
-$14,560/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="G40" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$470万
-$14,560/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="H40" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$490万
-$14,836/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="65" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B41" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$654万
-$14,772/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="C41" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$731万
-$14,772/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D41" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$653万
-$14,406/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E41" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$630万
-$14,428/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F41" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$470万
-$14,536/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="G41" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$470万
-$14,536/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="H41" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$489万
-$14,809/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="65" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B42" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$653万
-$14,745/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C42" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$730万
-$14,745/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D42" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$651万
-$14,377/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E42" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$629万
-$14,400/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F42" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$468万
-$14,480/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G42" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$469万
-$14,508/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="H42" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$488万
-$14,782/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="65" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B43" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$652万
-$14,718/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$729万
-$14,719/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D43" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$650万
-$14,353/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E43" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$628万
-$14,375/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F43" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$467万
-$14,455/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G43" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$468万
-$14,483/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="H43" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$487万
-$14,758/呎
-(25年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="65" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B44" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$651万
-$14,693/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C44" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$727万
-$14,693/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D44" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$649万
-$14,327/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E44" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$627万
-$14,348/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="F44" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$467万
-$14,458/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="G44" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$467万
-$14,458/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="H44" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$486万
-$14,730/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="65" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B45" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$650万
-$14,666/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C45" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$726万
-$14,667/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D45" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$648万
-$14,302/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E45" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$633万
-$14,485/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F45" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$466万
-$14,430/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="G45" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$466万
-$14,430/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="H45" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$485万
-$14,703/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="65" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B46" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$648万
-$14,639/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="C46" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$725万
-$14,638/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="D46" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$647万
-$14,276/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="E46" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$625万
-$14,297/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="F46" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$464万
-$14,375/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G46" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$465万
-$14,406/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="H46" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$484万
-$14,676/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="65" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B47" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$647万
-$14,614/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C47" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$723万
-$14,612/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="D47" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$646万
-$14,249/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="E47" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$624万
-$14,272/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="F47" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$464万
-$14,350/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G47" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$464万
-$14,378/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="H47" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$483万
-$14,648/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="65" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B48" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$645万
-$14,560/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C48" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$721万
-$14,562/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D48" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$643万
-$14,199/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="E48" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$621万
-$14,220/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="F48" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$463万
-$14,328/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="G48" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$463万
-$14,328/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="H48" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$482万
-$14,597/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="65" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B49" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$644万
-$14,535/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C49" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$719万
-$14,533/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D49" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$642万
-$14,174/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E49" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$620万
-$14,197/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F49" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$461万
-$14,272/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G49" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$462万
-$14,303/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="H49" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$481万
-$14,570/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="65" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B50" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$641万
-$14,463/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C50" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$716万
-$14,471/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="D50" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$640万
-$14,132/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="E50" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$618万
-$14,151/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F50" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$483万
-$14,941/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G50" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$458万
-$14,167/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="H50" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$478万
-$14,479/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="65" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B51" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$640万
-$14,436/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C51" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$715万
-$14,442/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="D51" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$639万
-$14,102/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="E51" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$617万
-$14,124/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F51" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$456万
-$14,111/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G51" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$457万
-$14,139/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="H51" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$477万
-$14,448/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="65" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B52" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$638万
-$14,404/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C52" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$714万
-$14,414/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D52" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$638万
-$14,075/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="E52" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$616万
-$14,096/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F52" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$456万
-$14,111/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="G52" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$456万
-$14,111/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="H52" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$476万
-$14,421/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="65" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B53" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$637万
-$14,377/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C53" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$712万
-$14,386/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D53" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$636万
-$14,046/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="E53" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$615万
-$14,066/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="F53" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$455万
-$14,080/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="G53" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$455万
-$14,080/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="H53" s="19" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$606万
-$18,361/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="65" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B54" s="18" t="inlineStr">
-        <is>
-          <t>A | 443呎 (2房)
-$636万
-$14,348/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C54" s="18" t="inlineStr">
-        <is>
-          <t>B | 495呎 (2房)
-$711万
-$14,356/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D54" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$635万
-$14,020/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E54" s="18" t="inlineStr">
-        <is>
-          <t>D | 437呎 (2房)
-$614万
-$14,039/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="F54" s="18" t="inlineStr">
-        <is>
-          <t>E | 323呎 (1房)
-$453万
-$14,028/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G54" s="18" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$454万
-$14,056/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="H54" s="18" t="inlineStr">
-        <is>
-          <t>G | 330呎 (1房)
-$474万
-$14,361/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="65" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B55" s="18" t="inlineStr">
-        <is>
-          <t>A | 408呎 (2房)
-$735万
-$18,017/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C55" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$801万
-$17,532/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D55" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$634万
-$13,989/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E55" s="19" t="inlineStr">
-        <is>
-          <t>D | 399呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F55" s="18" t="inlineStr">
-        <is>
-          <t>E | 286呎 (1房)
-$507万
-$17,734/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="G55" s="19" t="inlineStr">
-        <is>
-          <t>F | 285呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H55" s="19" t="inlineStr">
-        <is>
-          <t>G | 290呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G55"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Grand Seasons - 1B座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>300 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>291 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>66/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,577万
-$22,028/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$998万
-$21,832/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$961万
-$21,214/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$872万
-$20,057/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$629万
-$19,531/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$966万
-$21,551/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>65/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,236万
-$17,261/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$723万
-$15,825/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$717万
-$15,826/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$684万
-$15,729/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$508万
-$15,767/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$715万
-$15,962/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>63/F</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,594万
-$22,261/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$734万
-$16,066/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$728万
-$16,066/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$683万
-$15,703/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$507万
-$15,742/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$714万
-$15,933/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>62/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,216万
-$16,978/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$733万
-$16,037/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$718万
-$15,861/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$678万
-$15,589/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$506万
-$15,714/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$713万
-$15,908/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>61/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,210万
-$16,901/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$732万
-$16,011/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$717万
-$15,832/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$681万
-$15,651/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$502万
-$15,602/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$715万
-$15,969/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>60/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,187万
-$16,582/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$730万
-$15,985/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$716万
-$15,808/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$664万
-$15,276/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$493万
-$15,314/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$710万
-$15,855/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>59/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,192万
-$16,641/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$729万
-$15,956/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$719万
-$15,868/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$675万
-$15,510/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$504万
-$15,637/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$713万
-$15,915/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>58/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,210万
-$16,897/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$724万
-$15,840/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$714万
-$15,755/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$677万
-$15,570/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$497万
-$15,435/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$708万
-$15,801/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>57/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,191万
-$16,640/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$722万
-$15,788/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$715万
-$15,788/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$671万
-$15,432/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$495万
-$15,382/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$706万
-$15,748/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>56/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,182万
-$16,511/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$720万
-$15,761/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$710万
-$15,673/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$670万
-$15,405/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$489万
-$15,186/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$704万
-$15,719/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>55/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,173万
-$16,384/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$707万
-$15,470/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$705万
-$15,558/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$665万
-$15,292/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$491万
-$15,245/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$703万
-$15,694/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>53/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,171万
-$16,349/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$710万
-$15,532/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$704万
-$15,532/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$664万
-$15,267/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$487万
-$15,134/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$702万
-$15,665/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>52/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,175万
-$16,408/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$717万
-$15,681/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$706万
-$15,594/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$659万
-$15,156/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$486万
-$15,109/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$701万
-$15,641/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>51/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,172万
-$16,373/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$707万
-$15,479/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$705万
-$15,567/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$658万
-$15,129/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$486万
-$15,081/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$696万
-$15,527/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>50/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,183万
-$16,524/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$706万
-$15,453/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$704万
-$15,541/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$661万
-$15,191/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$485万
-$15,056/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$698万
-$15,587/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>48/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,161万
-$16,221/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$701万
-$15,341/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$703万
-$15,514/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$652万
-$14,995/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$484万
-$15,031/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$693万
-$15,473/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>47/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,171万
-$16,351/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$699万
-$15,289/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$700万
-$15,461/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$650万
-$14,945/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$482万
-$14,981/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$695万
-$15,507/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>46/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,169万
-$16,324/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$709万
-$15,523/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$699万
-$15,435/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$649万
-$14,920/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$482万
-$14,957/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G23" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$694万
-$15,482/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>45/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,173万
-$16,387/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$708万
-$15,497/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$702万
-$15,494/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$648万
-$14,894/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$481万
-$14,941/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G24" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$692万
-$15,455/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>43/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,165万
-$16,265/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$699万
-$15,293/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$697万
-$15,380/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$647万
-$14,867/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$480万
-$14,919/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G25" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$691万
-$15,426/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>42/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,176万
-$16,419/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$706万
-$15,440/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$695万
-$15,351/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$646万
-$14,839/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$480万
-$14,901/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="G26" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$686万
-$15,312/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,167万
-$16,299/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$692万
-$15,153/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$694万
-$15,325/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$644万
-$14,814/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$479万
-$14,885/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G27" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$685万
-$15,286/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,165万
-$16,270/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$691万
-$15,127/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$689万
-$15,210/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$643万
-$14,786/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$479万
-$14,866/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G28" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$684万
-$15,257/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,143万
-$15,968/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$690万
-$15,101/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$688万
-$15,183/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$642万
-$14,761/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$478万
-$14,851/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="G29" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$682万
-$15,230/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,148万
-$16,029/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$689万
-$15,072/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$686万
-$15,155/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$641万
-$14,736/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="F30" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$478万
-$14,829/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="G30" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$677万
-$15,118/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,150万
-$16,061/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$686万
-$15,020/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D31" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$684万
-$15,104/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E31" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$639万
-$14,680/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="F31" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$476万
-$14,795/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="G31" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$679万
-$15,150/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,135万
-$15,853/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$685万
-$14,991/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="D32" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$683万
-$15,075/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$637万
-$14,653/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="F32" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$476万
-$14,770/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="G32" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$677万
-$15,121/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B33" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,140万
-$15,915/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$684万
-$14,965/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D33" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$682万
-$15,049/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E33" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$636万
-$14,628/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="F33" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$475万
-$14,742/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="G33" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$672万
-$15,009/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,131万
-$15,796/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$683万
-$14,939/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D34" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$680万
-$15,020/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E34" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$635万
-$14,600/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="F34" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$474万
-$14,714/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="G34" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$675万
-$15,067/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B35" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,129万
-$15,768/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$681万
-$14,910/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D35" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$679万
-$14,993/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E35" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$634万
-$14,575/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F35" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$473万
-$14,689/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="G35" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$674万
-$15,040/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B36" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,127万
-$15,740/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$680万
-$14,884/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="D36" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$678万
-$14,967/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E36" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$633万
-$14,549/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F36" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$472万
-$14,665/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="G36" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$673万
-$15,013/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B37" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,125万
-$15,716/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$679万
-$14,862/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D37" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$673万
-$14,861/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E37" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$633万
-$14,556/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="F37" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$472万
-$14,668/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G37" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$672万
-$14,991/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B38" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,123万
-$15,689/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$678万
-$14,836/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="D38" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$672万
-$14,834/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E38" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$645万
-$14,832/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="F38" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$470万
-$14,612/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G38" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$667万
-$14,879/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B39" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,121万
-$15,661/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="C39" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$677万
-$14,810/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="D39" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$671万
-$14,808/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E39" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$630万
-$14,476/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F39" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$470万
-$14,584/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G39" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$665万
-$14,853/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="65" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B40" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,117万
-$15,603/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C40" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$674万
-$14,757/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D40" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$668万
-$14,755/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E40" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$636万
-$14,616/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="F40" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$469万
-$14,562/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="G40" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$667万
-$14,882/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="65" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B41" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,115万
-$15,575/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="C41" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$673万
-$14,731/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="D41" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$667万
-$14,728/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E41" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$635万
-$14,591/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F41" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$468万
-$14,534/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="G41" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$662万
-$14,772/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="65" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B42" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,113万
-$15,547/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="C42" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$672万
-$14,702/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="D42" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$666万
-$14,702/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E42" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$625万
-$14,372/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="F42" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$466万
-$14,481/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G42" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$661万
-$14,746/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="65" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B43" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,111万
-$15,520/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$671万
-$14,678/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D43" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$665万
-$14,675/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E43" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$624万
-$14,347/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F43" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$465万
-$14,453/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G43" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$663万
-$14,804/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="65" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B44" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,122万
-$15,668/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="C44" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$670万
-$14,652/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D44" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$664万
-$14,649/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E44" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$624万
-$14,347/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F44" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$466万
-$14,457/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="G44" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$658万
-$14,692/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="65" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B45" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,107万
-$15,464/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="C45" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$668万
-$14,624/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="D45" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$662万
-$14,623/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E45" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$623万
-$14,324/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F45" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$465万
-$14,432/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="G45" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$657万
-$14,667/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="65" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B46" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,105万
-$15,436/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="C46" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$667万
-$14,600/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="D46" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$661万
-$14,596/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E46" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$621万
-$14,269/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F46" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$463万
-$14,376/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G46" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$656万
-$14,641/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="65" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B47" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,103万
-$15,408/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="C47" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$666万
-$14,571/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D47" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$660万
-$14,570/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E47" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$620万
-$14,244/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F47" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$462万
-$14,348/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G47" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$655万
-$14,614/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="65" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B48" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,099万
-$15,353/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C48" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$664万
-$14,521/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D48" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$658万
-$14,519/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E48" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$619万
-$14,221/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="F48" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$461万
-$14,326/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="G48" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$652万
-$14,562/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="65" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B49" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,097万
-$15,325/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="C49" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$662万
-$14,492/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D49" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$656万
-$14,492/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E49" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$630万
-$14,487/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F49" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$460万
-$14,273/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G49" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$651万
-$14,536/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="65" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B50" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,096万
-$15,314/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C50" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$660万
-$14,449/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D50" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$753万
-$16,618/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E50" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$614万
-$14,124/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="F50" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$455万
-$14,140/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G50" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$648万
-$14,462/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="65" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B51" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,094万
-$15,284/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C51" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$659万
-$14,420/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D51" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$653万
-$14,419/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E51" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$613万
-$14,094/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="F51" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$454万
-$14,109/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G51" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$650万
-$14,516/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="65" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B52" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,098万
-$15,339/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C52" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$658万
-$14,392/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D52" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$652万
-$14,391/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E52" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$613万
-$14,094/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="F52" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$454万
-$14,109/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="G52" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$649万
-$14,487/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="65" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B53" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,102万
-$15,394/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C53" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$660万
-$14,444/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D53" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$654万
-$14,444/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E53" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$612万
-$14,067/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="F53" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$453万
-$14,081/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="G53" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$648万
-$14,458/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="65" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B54" s="18" t="inlineStr">
-        <is>
-          <t>A | 716呎 (3房)
-$1,106万
-$15,448/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C54" s="18" t="inlineStr">
-        <is>
-          <t>B | 457呎 (2房)
-$662万
-$14,497/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D54" s="18" t="inlineStr">
-        <is>
-          <t>C | 453呎 (2房)
-$657万
-$14,497/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E54" s="18" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-$623万
-$14,329/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="F54" s="18" t="inlineStr">
-        <is>
-          <t>E | 322呎 (1房)
-$452万
-$14,028/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G54" s="18" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-$650万
-$14,511/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="65" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B55" s="18" t="inlineStr">
-        <is>
-          <t>A | 678呎 (3房)
-$1,153万
-$17,009/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="C55" s="19" t="inlineStr">
-        <is>
-          <t>B | 419呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D55" s="18" t="inlineStr">
-        <is>
-          <t>C | 415呎 (2房)
-$730万
-$17,588/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E55" s="18" t="inlineStr">
-        <is>
-          <t>D | 399呎 (2房)
-$704万
-$17,649/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="F55" s="18" t="inlineStr">
-        <is>
-          <t>E | 399呎 (1房)
-$507万
-$12,712/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G55" s="19" t="inlineStr">
-        <is>
-          <t>F | 408呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-将军澳-Grand Seasons.xlsx
+++ b/files/九龙-将军澳-Grand Seasons.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +43,102 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +149,36 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +224,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +654,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -30465,4 +30645,6180 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$947万
+$21,372/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$1034万
+$20,881/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$918万
+$20,269/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$896万
+$20,515/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$662万
+$20,486/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$650万
+$20,121/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$728万
+$22,064/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$715万
+$16,140/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$781万
+$15,784/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$717万
+$15,828/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$684万
+$15,645/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$498万
+$15,418/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$507万
+$15,684/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$528万
+$16,003/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$714万
+$16,111/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$780万
+$15,758/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$716万
+$15,799/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$686万
+$15,705/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$503万
+$15,567/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$503万
+$15,570/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H7" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$609万
+$18,448/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$713万
+$16,086/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$779万
+$15,731/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$714万
+$15,773/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$670万
+$15,330/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$499万
+$15,455/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$505万
+$15,628/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$526万
+$15,945/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$711万
+$16,056/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$777万
+$15,705/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$713万
+$15,746/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$684万
+$15,652/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$496万
+$15,341/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$507万
+$15,690/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$525万
+$15,918/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$706万
+$15,941/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$776万
+$15,677/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$712万
+$15,720/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$683万
+$15,625/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$500万
+$15,489/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$503万
+$15,576/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$524万
+$15,891/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$709万
+$16,005/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$775万
+$15,651/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$707万
+$15,607/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$678万
+$15,513/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$497万
+$15,375/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$502万
+$15,551/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$524万
+$15,864/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$704万
+$15,887/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$773万
+$15,624/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$710万
+$15,667/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$677万
+$15,487/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$496万
+$15,350/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$499万
+$15,437/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$520万
+$15,748/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$702万
+$15,835/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$771万
+$15,572/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$707万
+$15,614/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$663万
+$15,174/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$494万
+$15,297/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$494万
+$15,297/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$521万
+$15,785/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$700万
+$15,806/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$770万
+$15,545/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$702万
+$15,499/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$670万
+$15,320/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$493万
+$15,272/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$491万
+$15,189/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$520万
+$15,761/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$687万
+$15,515/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$768万
+$15,519/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$701万
+$15,475/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$661万
+$15,121/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$490万
+$15,161/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$492万
+$15,248/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$516万
+$15,645/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$686万
+$15,490/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$767万
+$15,493/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$684万
+$15,104/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$660万
+$15,098/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$492万
+$15,220/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$489万
+$15,136/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$512万
+$15,530/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$685万
+$15,463/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$766万
+$15,467/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$699万
+$15,422/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$659万
+$15,071/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$491万
+$15,195/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$488万
+$15,108/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$514万
+$15,591/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$684万
+$15,436/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$764万
+$15,438/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$694万
+$15,311/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$658万
+$15,046/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$490万
+$15,167/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$487万
+$15,084/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$514万
+$15,564/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$686万
+$15,497/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$763万
+$15,414/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$685万
+$15,113/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$656万
+$15,021/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$486万
+$15,056/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$489万
+$15,146/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$513万
+$15,536/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$685万
+$15,472/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$762万
+$15,388/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$691万
+$15,258/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$655万
+$14,995/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$486万
+$15,031/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$486万
+$15,031/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$509万
+$15,424/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$683万
+$15,420/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$759万
+$15,335/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$677万
+$14,951/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$653万
+$14,945/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$484万
+$14,981/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$487万
+$15,068/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$507万
+$15,373/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$682万
+$15,393/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$758万
+$15,307/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$688万
+$15,183/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$652万
+$14,920/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$483万
+$14,957/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$483万
+$14,957/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$509万
+$15,433/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$677万
+$15,280/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$756万
+$15,281/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$675万
+$14,901/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$651万
+$14,895/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$483万
+$14,941/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$485万
+$15,025/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$508万
+$15,406/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$680万
+$15,341/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$755万
+$15,253/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$674万
+$14,874/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$650万
+$14,867/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$482万
+$14,920/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$482万
+$14,920/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$505万
+$15,291/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$678万
+$15,312/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$754万
+$15,226/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$673万
+$14,848/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$648万
+$14,840/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$481万
+$14,901/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$481万
+$14,901/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$506万
+$15,348/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$673万
+$15,196/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$752万
+$15,198/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$671万
+$14,821/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$647万
+$14,815/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$481万
+$14,885/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$481万
+$14,885/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$506万
+$15,324/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$676万
+$15,257/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$751万
+$15,172/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$670万
+$14,795/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$646万
+$14,787/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$480万
+$14,867/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$480万
+$14,867/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$505万
+$15,297/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$671万
+$15,144/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$750万
+$15,143/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$669万
+$14,766/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$645万
+$14,760/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$480万
+$14,848/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$480万
+$14,848/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$504万
+$15,267/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$670万
+$15,115/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$748万
+$15,115/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$668万
+$14,742/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$644万
+$14,735/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$479万
+$14,830/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$479万
+$14,830/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H29" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$500万
+$15,155/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$667万
+$15,063/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$746万
+$15,063/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$665万
+$14,689/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$642万
+$14,682/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$478万
+$14,796/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$478万
+$14,796/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H30" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$501万
+$15,185/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$666万
+$15,034/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$744万
+$15,036/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$664万
+$14,662/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$640万
+$14,654/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$477万
+$14,768/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="G31" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$477万
+$14,768/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H31" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$497万
+$15,073/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$665万
+$15,009/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$743万
+$15,008/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$663万
+$14,636/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$639万
+$14,629/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$476万
+$14,743/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="G32" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$476万
+$14,743/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H32" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$499万
+$15,130/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$664万
+$14,982/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$742万
+$14,980/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$662万
+$14,609/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$638万
+$14,602/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F33" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$475万
+$14,715/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="G33" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$481万
+$14,882/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="H33" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$496万
+$15,018/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$662万
+$14,953/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$740万
+$14,954/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$661万
+$14,583/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$637万
+$14,577/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F34" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$474万
+$14,690/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G34" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$474万
+$14,690/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="H34" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$498万
+$15,076/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$661万
+$14,928/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$739万
+$14,927/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$659万
+$14,556/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$636万
+$14,556/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$474万
+$14,669/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="G35" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$474万
+$14,669/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="H35" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$494万
+$14,964/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$660万
+$14,905/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$738万
+$14,905/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$658万
+$14,536/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$636万
+$14,549/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$474万
+$14,666/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$474万
+$14,666/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="H36" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$493万
+$14,942/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$659万
+$14,878/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$736万
+$14,879/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$657万
+$14,508/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$635万
+$14,531/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$472万
+$14,610/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$473万
+$14,641/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="H37" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$492万
+$14,915/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$751万
+$16,955/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C38" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$735万
+$14,851/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="D38" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$656万
+$14,483/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E38" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$634万
+$14,503/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F38" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$471万
+$14,585/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$472万
+$14,613/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H38" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$491万
+$14,891/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B39" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$656万
+$14,799/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C39" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$732万
+$14,798/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D39" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$654万
+$14,430/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E39" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$632万
+$14,453/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F39" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$470万
+$14,560/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G39" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$470万
+$14,560/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="H39" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$490万
+$14,836/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="58" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$654万
+$14,772/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C40" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$731万
+$14,772/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D40" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$653万
+$14,406/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E40" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$630万
+$14,428/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F40" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$470万
+$14,536/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G40" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$470万
+$14,536/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H40" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$489万
+$14,809/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="58" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$653万
+$14,745/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C41" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$730万
+$14,745/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D41" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$651万
+$14,377/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E41" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$629万
+$14,400/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F41" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$468万
+$14,480/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G41" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$469万
+$14,508/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H41" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$488万
+$14,782/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="58" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$652万
+$14,718/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C42" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$729万
+$14,719/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D42" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$650万
+$14,353/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E42" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$628万
+$14,375/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F42" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$467万
+$14,455/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G42" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$468万
+$14,483/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H42" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$487万
+$14,758/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="58" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$651万
+$14,693/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C43" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$727万
+$14,693/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D43" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$649万
+$14,327/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E43" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$627万
+$14,348/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F43" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$467万
+$14,458/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G43" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$467万
+$14,458/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H43" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$486万
+$14,730/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="58" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$650万
+$14,666/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C44" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$726万
+$14,667/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D44" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$648万
+$14,302/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E44" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$633万
+$14,485/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F44" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$466万
+$14,430/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G44" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$466万
+$14,430/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H44" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$485万
+$14,703/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="58" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$648万
+$14,639/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C45" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$725万
+$14,638/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="D45" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$647万
+$14,276/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E45" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$625万
+$14,297/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F45" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$464万
+$14,375/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G45" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$465万
+$14,406/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H45" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$484万
+$14,676/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="58" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$647万
+$14,614/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C46" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$723万
+$14,612/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D46" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$646万
+$14,249/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="E46" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$624万
+$14,272/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F46" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$464万
+$14,350/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G46" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$464万
+$14,378/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H46" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$483万
+$14,648/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="58" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B47" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$645万
+$14,560/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C47" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$721万
+$14,562/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D47" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$643万
+$14,199/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E47" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$621万
+$14,220/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F47" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$463万
+$14,328/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G47" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$463万
+$14,328/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H47" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$482万
+$14,597/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="58" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$644万
+$14,535/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C48" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$719万
+$14,533/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D48" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$642万
+$14,174/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E48" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$620万
+$14,197/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F48" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$461万
+$14,272/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G48" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$462万
+$14,303/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H48" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$481万
+$14,570/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="58" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$641万
+$14,463/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C49" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$716万
+$14,471/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D49" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$640万
+$14,132/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E49" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$618万
+$14,151/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F49" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$483万
+$14,941/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G49" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$458万
+$14,167/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H49" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$478万
+$14,479/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="58" customHeight="1">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$640万
+$14,436/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C50" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$715万
+$14,442/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="D50" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$639万
+$14,102/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E50" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$617万
+$14,124/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F50" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$456万
+$14,111/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G50" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$457万
+$14,139/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H50" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$477万
+$14,448/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="58" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$638万
+$14,404/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C51" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$714万
+$14,414/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D51" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$638万
+$14,075/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E51" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$616万
+$14,096/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F51" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$456万
+$14,111/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G51" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$456万
+$14,111/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H51" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$476万
+$14,421/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="58" customHeight="1">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$637万
+$14,377/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C52" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$712万
+$14,386/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D52" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$636万
+$14,046/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E52" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$615万
+$14,066/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F52" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$455万
+$14,080/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G52" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$455万
+$14,080/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H52" s="23" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$606万
+$18,361/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="58" customHeight="1">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B53" s="22" t="inlineStr">
+        <is>
+          <t>A | 443呎 (2房)
+$636万
+$14,348/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C53" s="22" t="inlineStr">
+        <is>
+          <t>B | 495呎 (2房)
+$711万
+$14,356/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D53" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$635万
+$14,020/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E53" s="22" t="inlineStr">
+        <is>
+          <t>D | 437呎 (2房)
+$614万
+$14,039/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F53" s="22" t="inlineStr">
+        <is>
+          <t>E | 323呎 (1房)
+$453万
+$14,028/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G53" s="22" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$454万
+$14,056/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="H53" s="22" t="inlineStr">
+        <is>
+          <t>G | 330呎 (1房)
+$474万
+$14,361/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="58" customHeight="1">
+      <c r="A54" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B54" s="22" t="inlineStr">
+        <is>
+          <t>A | 408呎 (2房)
+$735万
+$18,017/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C54" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$801万
+$17,532/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D54" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$634万
+$13,989/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E54" s="23" t="inlineStr">
+        <is>
+          <t>D | 399呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F54" s="22" t="inlineStr">
+        <is>
+          <t>E | 286呎 (1房)
+$507万
+$17,734/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="G54" s="23" t="inlineStr">
+        <is>
+          <t>F | 285呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H54" s="23" t="inlineStr">
+        <is>
+          <t>G | 290呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1577万
+$22,028/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$998万
+$21,832/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$961万
+$21,214/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$872万
+$20,057/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$629万
+$19,531/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$966万
+$21,551/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1236万
+$17,261/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$723万
+$15,825/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$717万
+$15,826/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$684万
+$15,729/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$508万
+$15,767/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$715万
+$15,962/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1594万
+$22,261/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$734万
+$16,066/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$728万
+$16,066/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$683万
+$15,703/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$507万
+$15,742/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$714万
+$15,933/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1216万
+$16,978/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$733万
+$16,037/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$718万
+$15,861/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$678万
+$15,589/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$506万
+$15,714/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$713万
+$15,908/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1210万
+$16,901/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$732万
+$16,011/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$717万
+$15,832/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$681万
+$15,651/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$502万
+$15,602/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$715万
+$15,969/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1187万
+$16,582/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$730万
+$15,985/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$716万
+$15,808/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$664万
+$15,276/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$493万
+$15,314/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$710万
+$15,855/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1192万
+$16,641/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$729万
+$15,956/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$719万
+$15,868/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$675万
+$15,510/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$504万
+$15,637/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$713万
+$15,915/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1210万
+$16,897/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$724万
+$15,840/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$714万
+$15,755/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$677万
+$15,570/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$497万
+$15,435/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$708万
+$15,801/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1191万
+$16,640/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$722万
+$15,788/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$715万
+$15,788/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$671万
+$15,432/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$495万
+$15,382/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$706万
+$15,748/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1182万
+$16,511/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$720万
+$15,761/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$710万
+$15,673/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$670万
+$15,405/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$489万
+$15,186/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$704万
+$15,719/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1173万
+$16,384/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$707万
+$15,470/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$705万
+$15,558/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$665万
+$15,292/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$491万
+$15,245/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$703万
+$15,694/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1171万
+$16,349/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$710万
+$15,532/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$704万
+$15,532/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$664万
+$15,267/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$487万
+$15,134/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$702万
+$15,665/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1175万
+$16,408/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$717万
+$15,681/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$706万
+$15,594/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$659万
+$15,156/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$486万
+$15,109/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$701万
+$15,641/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1172万
+$16,373/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$707万
+$15,479/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$705万
+$15,567/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$658万
+$15,129/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$486万
+$15,081/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$696万
+$15,527/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1183万
+$16,524/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$706万
+$15,453/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$704万
+$15,541/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$661万
+$15,191/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$485万
+$15,056/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$698万
+$15,587/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1161万
+$16,221/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$701万
+$15,341/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$703万
+$15,514/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$652万
+$14,995/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$484万
+$15,031/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$693万
+$15,473/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1171万
+$16,351/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$699万
+$15,289/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$700万
+$15,461/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$650万
+$14,945/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$482万
+$14,981/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$695万
+$15,507/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1169万
+$16,324/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$709万
+$15,523/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$699万
+$15,435/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$649万
+$14,920/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$482万
+$14,957/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$694万
+$15,482/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1173万
+$16,387/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$708万
+$15,497/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$702万
+$15,494/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$648万
+$14,894/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$481万
+$14,941/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$692万
+$15,455/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1165万
+$16,265/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$699万
+$15,293/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$697万
+$15,380/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$647万
+$14,867/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$480万
+$14,919/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$691万
+$15,426/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1176万
+$16,419/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$706万
+$15,440/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$695万
+$15,351/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$646万
+$14,839/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$480万
+$14,901/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$686万
+$15,312/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1167万
+$16,299/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$692万
+$15,153/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$694万
+$15,325/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$644万
+$14,814/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$479万
+$14,885/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$685万
+$15,286/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1165万
+$16,270/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$691万
+$15,127/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$689万
+$15,210/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$643万
+$14,786/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$479万
+$14,866/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$684万
+$15,257/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1143万
+$15,968/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$690万
+$15,101/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$688万
+$15,183/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$642万
+$14,761/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$478万
+$14,851/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$682万
+$15,230/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1148万
+$16,029/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$689万
+$15,072/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$686万
+$15,155/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$641万
+$14,736/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$478万
+$14,829/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$677万
+$15,118/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1150万
+$16,061/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$686万
+$15,020/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$684万
+$15,104/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$639万
+$14,680/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$476万
+$14,795/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$679万
+$15,150/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1135万
+$15,853/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$685万
+$14,991/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$683万
+$15,075/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$637万
+$14,653/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$476万
+$14,770/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G31" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$677万
+$15,121/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1140万
+$15,915/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$684万
+$14,965/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$682万
+$15,049/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$636万
+$14,628/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$475万
+$14,742/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G32" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$672万
+$15,009/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1131万
+$15,796/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$683万
+$14,939/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$680万
+$15,020/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$635万
+$14,600/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F33" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$474万
+$14,714/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G33" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$675万
+$15,067/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1129万
+$15,768/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$681万
+$14,910/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$679万
+$14,993/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$634万
+$14,575/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F34" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$473万
+$14,689/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G34" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$674万
+$15,040/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1127万
+$15,740/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$680万
+$14,884/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$678万
+$14,967/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$633万
+$14,549/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$472万
+$14,665/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G35" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$673万
+$15,013/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1125万
+$15,716/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$679万
+$14,862/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$673万
+$14,861/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$633万
+$14,556/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$472万
+$14,668/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$672万
+$14,991/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1123万
+$15,689/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$678万
+$14,836/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$672万
+$14,834/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$645万
+$14,832/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$470万
+$14,612/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$667万
+$14,879/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1121万
+$15,661/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C38" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$677万
+$14,810/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D38" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$671万
+$14,808/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E38" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$630万
+$14,476/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F38" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$470万
+$14,584/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$665万
+$14,853/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B39" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1117万
+$15,603/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C39" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$674万
+$14,757/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D39" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$668万
+$14,755/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E39" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$636万
+$14,616/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F39" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$469万
+$14,562/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="G39" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$667万
+$14,882/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="58" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1115万
+$15,575/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C40" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$673万
+$14,731/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D40" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$667万
+$14,728/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E40" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$635万
+$14,591/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F40" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$468万
+$14,534/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="G40" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$662万
+$14,772/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="58" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1113万
+$15,547/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C41" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$672万
+$14,702/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D41" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$666万
+$14,702/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E41" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$625万
+$14,372/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F41" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$466万
+$14,481/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G41" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$661万
+$14,746/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="58" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1111万
+$15,520/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C42" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$671万
+$14,678/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D42" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$665万
+$14,675/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E42" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$624万
+$14,347/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F42" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$465万
+$14,453/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G42" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$663万
+$14,804/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="58" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1122万
+$15,668/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C43" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$670万
+$14,652/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D43" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$664万
+$14,649/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E43" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$624万
+$14,347/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F43" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$466万
+$14,457/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="G43" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$658万
+$14,692/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="58" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1107万
+$15,464/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C44" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$668万
+$14,624/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D44" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$662万
+$14,623/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E44" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$623万
+$14,324/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F44" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$465万
+$14,432/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="G44" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$657万
+$14,667/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="58" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1105万
+$15,436/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C45" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$667万
+$14,600/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="D45" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$661万
+$14,596/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E45" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$621万
+$14,269/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F45" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$463万
+$14,376/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G45" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$656万
+$14,641/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="58" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1103万
+$15,408/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C46" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$666万
+$14,571/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D46" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$660万
+$14,570/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E46" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$620万
+$14,244/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F46" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$462万
+$14,348/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G46" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$655万
+$14,614/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="58" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B47" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1099万
+$15,353/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C47" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$664万
+$14,521/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D47" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$658万
+$14,519/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E47" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$619万
+$14,221/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F47" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$461万
+$14,326/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G47" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$652万
+$14,562/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="58" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1097万
+$15,325/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C48" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$662万
+$14,492/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D48" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$656万
+$14,492/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E48" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$630万
+$14,487/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F48" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$460万
+$14,273/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G48" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$651万
+$14,536/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="58" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1096万
+$15,314/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C49" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$660万
+$14,449/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D49" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$753万
+$16,618/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="E49" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$614万
+$14,124/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F49" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$455万
+$14,140/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G49" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$648万
+$14,462/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="58" customHeight="1">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1094万
+$15,284/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C50" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$659万
+$14,420/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D50" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$653万
+$14,419/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E50" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$613万
+$14,094/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F50" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$454万
+$14,109/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G50" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$650万
+$14,516/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="58" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1098万
+$15,339/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C51" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$658万
+$14,392/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D51" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$652万
+$14,391/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E51" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$613万
+$14,094/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F51" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$454万
+$14,109/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G51" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$649万
+$14,487/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="58" customHeight="1">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1102万
+$15,394/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C52" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$660万
+$14,444/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D52" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$654万
+$14,444/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E52" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$612万
+$14,067/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F52" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$453万
+$14,081/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="G52" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$648万
+$14,458/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="58" customHeight="1">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B53" s="22" t="inlineStr">
+        <is>
+          <t>A | 716呎 (3房)
+$1106万
+$15,448/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C53" s="22" t="inlineStr">
+        <is>
+          <t>B | 457呎 (2房)
+$662万
+$14,497/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D53" s="22" t="inlineStr">
+        <is>
+          <t>C | 453呎 (2房)
+$657万
+$14,497/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E53" s="22" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+$623万
+$14,329/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F53" s="22" t="inlineStr">
+        <is>
+          <t>E | 322呎 (1房)
+$452万
+$14,028/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G53" s="22" t="inlineStr">
+        <is>
+          <t>F | 448呎 (2房)
+$650万
+$14,511/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="58" customHeight="1">
+      <c r="A54" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B54" s="22" t="inlineStr">
+        <is>
+          <t>A | 678呎 (3房)
+$1153万
+$17,009/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C54" s="23" t="inlineStr">
+        <is>
+          <t>B | 419呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D54" s="22" t="inlineStr">
+        <is>
+          <t>C | 415呎 (2房)
+$730万
+$17,588/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E54" s="22" t="inlineStr">
+        <is>
+          <t>D | 399呎 (2房)
+$704万
+$17,649/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F54" s="22" t="inlineStr">
+        <is>
+          <t>E | 399呎 (1房)
+$507万
+$12,712/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G54" s="23" t="inlineStr">
+        <is>
+          <t>F | 408呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-将军澳-Grand Seasons.xlsx
+++ b/files/九龙-将军澳-Grand Seasons.xlsx
@@ -654,7 +654,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
